--- a/engine/datasheet/datasheet_template.xlsx
+++ b/engine/datasheet/datasheet_template.xlsx
@@ -4,14 +4,27 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="12420"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="预制件模板" sheetId="2" r:id="rId1"/>
     <sheet name="标准模板" sheetId="3" r:id="rId2"/>
     <sheet name="索引模板" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -88,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
   <si>
     <t>数据表类型</t>
   </si>
@@ -111,7 +124,7 @@
     <t>通用奖励</t>
   </si>
   <si>
-    <t>{ id: int, count: int }</t>
+    <t>{ id: *int, count: int }</t>
   </si>
   <si>
     <t>PlayerAward</t>
@@ -121,6 +134,15 @@
   </si>
   <si>
     <t>{ id: string, awards: []Award }</t>
+  </si>
+  <si>
+    <t>Awards</t>
+  </si>
+  <si>
+    <t>一堆奖励</t>
+  </si>
+  <si>
+    <t>[]*Award</t>
   </si>
   <si>
     <t>standard</t>
@@ -207,7 +229,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -248,55 +270,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -341,6 +327,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -386,7 +387,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -418,49 +440,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -472,121 +578,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -623,21 +645,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -671,6 +678,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -727,148 +749,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -895,52 +917,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1211,8 +1233,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="22.2857142857143" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.5714285714286" style="1" customWidth="1"/>
@@ -1258,6 +1280,17 @@
       </c>
       <c r="C5" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1289,63 +1322,63 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="E6" s="1">
         <v>10000</v>
@@ -1353,7 +1386,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1 C1 D1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:D1">
       <formula1>"prefab,standard,index"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1380,62 +1413,62 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B7" s="4">
         <v>1</v>
@@ -1444,21 +1477,21 @@
         <v>2</v>
       </c>
       <c r="D7" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="2:4">
@@ -1469,7 +1502,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="2:4">
@@ -1480,7 +1513,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="2:4">
@@ -1491,7 +1524,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/engine/datasheet/datasheet_template.xlsx
+++ b/engine/datasheet/datasheet_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="预制件模板" sheetId="2" r:id="rId1"/>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="42">
   <si>
     <t>数据表类型</t>
   </si>
@@ -191,6 +191,9 @@
   </si>
   <si>
     <t>bigint</t>
+  </si>
+  <si>
+    <t>100000000000000000000000000000000000000000</t>
   </si>
   <si>
     <t>index</t>
@@ -912,6 +915,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1380,8 +1386,8 @@
       <c r="D6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="1">
-        <v>10000</v>
+      <c r="E6" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1399,7 +1405,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="22.2857142857143" style="1" customWidth="1"/>
@@ -1413,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1421,21 +1427,21 @@
         <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1443,13 +1449,13 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1457,10 +1463,10 @@
         <v>19</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>24</v>
@@ -1468,7 +1474,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="4">
         <v>1</v>
@@ -1524,6 +1530,39 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" s="1">
+        <v>10001</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" s="1">
+        <v>10001</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" s="1">
+        <v>10001</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>26</v>
       </c>
     </row>

--- a/engine/datasheet/datasheet_template.xlsx
+++ b/engine/datasheet/datasheet_template.xlsx
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
   <si>
     <t>数据表类型</t>
   </si>
@@ -196,6 +196,36 @@
     <t>100000000000000000000000000000000000000000</t>
   </si>
   <si>
+    <t>idx1</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>2024-11-11</t>
+  </si>
+  <si>
+    <t>idx2</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>idx3</t>
+  </si>
+  <si>
+    <t>*int</t>
+  </si>
+  <si>
+    <t>idx4</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>3.3h</t>
+  </si>
+  <si>
     <t>index</t>
   </si>
   <si>
@@ -221,9 +251,6 @@
   </si>
   <si>
     <t>awards</t>
-  </si>
-  <si>
-    <t>int</t>
   </si>
   <si>
     <t>索引顺序</t>
@@ -897,7 +924,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -917,7 +944,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1314,8 +1344,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="22.2857142857143" style="1" customWidth="1"/>
     <col min="2" max="3" width="20.5714285714286" style="1" customWidth="1"/>
@@ -1389,6 +1419,284 @@
       <c r="E6" s="7" t="s">
         <v>30</v>
       </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1419,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1427,21 +1735,21 @@
         <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1449,13 +1757,13 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1463,10 +1771,10 @@
         <v>19</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>24</v>
@@ -1474,7 +1782,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B7" s="4">
         <v>1</v>

--- a/engine/datasheet/datasheet_template.xlsx
+++ b/engine/datasheet/datasheet_template.xlsx
@@ -4,27 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="21435" windowHeight="10710" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="预制件模板" sheetId="2" r:id="rId1"/>
     <sheet name="标准模板" sheetId="3" r:id="rId2"/>
     <sheet name="索引模板" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -101,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="52">
   <si>
     <t>数据表类型</t>
   </si>
@@ -221,6 +208,9 @@
   </si>
   <si>
     <t>duration</t>
+  </si>
+  <si>
+    <t>c</t>
   </si>
   <si>
     <t>3.3h</t>
@@ -259,7 +249,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -300,6 +290,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -313,6 +331,14 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -357,14 +383,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -372,7 +391,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -380,6 +399,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -388,57 +414,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -470,13 +460,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,24 +526,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -530,18 +574,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -554,36 +586,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -602,24 +610,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -633,12 +629,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -675,6 +665,21 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -708,21 +713,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -779,148 +769,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -953,52 +943,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1482,10 +1472,10 @@
         <v>39</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1727,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1735,21 +1725,21 @@
         <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1757,13 +1747,13 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1782,7 +1772,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B7" s="4">
         <v>1</v>
